--- a/GPS-Speedsurfing_UsersEqLinks.xlsx
+++ b/GPS-Speedsurfing_UsersEqLinks.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B5D1E3-56B9-4E68-9170-74E2425373EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="4188" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7065" yWindow="5970" windowWidth="28410" windowHeight="14910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -294,11 +294,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -587,7 +586,7 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.85546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="3" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="0.28515625" style="2" customWidth="1"/>
     <col min="7" max="7" width="6.140625" customWidth="1"/>
@@ -595,22 +594,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="1"/>
@@ -619,7 +618,7 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -632,7 +631,7 @@
         <f t="shared" ref="E2:E5" si="0">HYPERLINK(_xlfn.CONCAT(F2,D2),B2)</f>
         <v>BQ</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H2" t="s">
@@ -643,7 +642,7 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
@@ -656,7 +655,7 @@
         <f t="shared" si="0"/>
         <v>Nilsson</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H3" t="s">
@@ -667,7 +666,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C4" t="s">
@@ -680,7 +679,7 @@
         <f t="shared" si="0"/>
         <v>Göransson</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H4" t="s">
@@ -691,7 +690,7 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
@@ -704,7 +703,7 @@
         <f t="shared" si="0"/>
         <v>Räkan</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H5" t="s">
@@ -715,7 +714,7 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
@@ -728,7 +727,7 @@
         <f>HYPERLINK(_xlfn.CONCAT(F6,D6),B6)</f>
         <v>Ungtuppen</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H6" t="s">
@@ -739,7 +738,7 @@
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
@@ -752,7 +751,7 @@
         <f t="shared" ref="E7:E21" si="1">HYPERLINK(_xlfn.CONCAT(F7,D7),B7)</f>
         <v>Jocke</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H7" t="s">
@@ -763,7 +762,7 @@
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C8" t="s">
@@ -776,7 +775,7 @@
         <f t="shared" si="1"/>
         <v>Örjan</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H8" t="s">
@@ -787,7 +786,7 @@
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
@@ -800,7 +799,7 @@
         <f t="shared" si="1"/>
         <v>Berra</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H9" t="s">
@@ -811,7 +810,7 @@
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C10" t="s">
@@ -824,7 +823,7 @@
         <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H10" t="s">
@@ -835,7 +834,7 @@
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
@@ -848,7 +847,7 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H11" t="s">
@@ -859,7 +858,7 @@
       <c r="A12" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
@@ -872,7 +871,7 @@
         <f t="shared" si="1"/>
         <v>Ultraräkan</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H12" t="s">
@@ -883,7 +882,7 @@
       <c r="A13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C13" t="s">
@@ -896,7 +895,7 @@
         <f t="shared" si="1"/>
         <v>Mogge</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H13" t="s">
@@ -907,7 +906,7 @@
       <c r="A14" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
@@ -920,7 +919,7 @@
         <f t="shared" si="1"/>
         <v>JesPer</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H14" t="s">
@@ -931,7 +930,7 @@
       <c r="A15" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C15" t="s">
@@ -944,7 +943,7 @@
         <f t="shared" si="1"/>
         <v>J&amp;B</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H15" t="s">
@@ -955,7 +954,7 @@
       <c r="A16" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C16" t="s">
@@ -968,7 +967,7 @@
         <f t="shared" si="1"/>
         <v>M1</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H16" t="s">
@@ -979,7 +978,7 @@
       <c r="A17" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C17" t="s">
@@ -992,7 +991,7 @@
         <f t="shared" si="1"/>
         <v>Ove</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H17" t="s">
@@ -1003,7 +1002,7 @@
       <c r="A18" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C18" t="s">
@@ -1016,7 +1015,7 @@
         <f t="shared" si="1"/>
         <v>EA</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H18" t="s">
@@ -1027,7 +1026,7 @@
       <c r="A19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C19" t="s">
@@ -1040,7 +1039,7 @@
         <f t="shared" si="1"/>
         <v>Budda</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H19" t="s">
@@ -1051,7 +1050,7 @@
       <c r="A20" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C20" t="s">
@@ -1064,7 +1063,7 @@
         <f t="shared" si="1"/>
         <v>Joko</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H20" t="s">
@@ -1075,7 +1074,7 @@
       <c r="A21" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C21" t="s">
@@ -1088,7 +1087,7 @@
         <f t="shared" si="1"/>
         <v>Harald</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H21" t="s">

--- a/GPS-Speedsurfing_UsersEqLinks.xlsx
+++ b/GPS-Speedsurfing_UsersEqLinks.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Documents\bjorn76\WS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B5D1E3-56B9-4E68-9170-74E2425373EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA11991-8B4F-46D7-B9C7-060ACDFE1CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7065" yWindow="5970" windowWidth="28410" windowHeight="14910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="User" sheetId="1" r:id="rId1"/>
+    <sheet name="Equipment" sheetId="2" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -584,16 +586,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="0.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" customWidth="1"/>
-    <col min="8" max="8" width="1.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="0.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" customWidth="1"/>
+    <col min="8" max="8" width="1.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
@@ -614,7 +616,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -638,7 +640,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -662,7 +664,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -686,7 +688,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -710,7 +712,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -734,7 +736,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -758,7 +760,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -782,7 +784,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -806,7 +808,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -830,7 +832,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -854,7 +856,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -878,7 +880,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -902,7 +904,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -926,7 +928,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -950,7 +952,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -974,7 +976,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -998,7 +1000,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1022,7 +1024,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1046,7 +1048,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1070,7 +1072,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -1097,4 +1099,22 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E8E445-90B6-496D-AEB6-772532BC7A87}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4CB837-2605-43E7-9B78-1877BF835445}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>